--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_04-06-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_04-06-2025.xlsx
@@ -538,54 +538,54 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>£11.15</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>£11.15</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>£11.15</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>£13.50</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>£11.40</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>£11.25</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>£11.25</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>£11.73</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>£13.49 presale price: £21.61</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>£11.18</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>£13.50</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>£11.40</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>£11.25</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>£11.73</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>£13.49 presale price: £21.61</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>£11.18</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>£11.18</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>£21.15</t>
@@ -608,7 +608,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/25mm-recticel-insulation (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000002163648AC90&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/25mm-recticel-insulation (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B7842F90&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -635,54 +635,54 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>£12.80</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>£12.80</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>£12.80</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>£17.95</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>£13.28</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>£13.15</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>£13.15</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>£13.86</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>£17.39 presale price: £26.0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>£12.84</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>£12.83</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>£17.95</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>£13.28</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>£13.15</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>£13.86</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>£17.39 presale price: £26.0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>£12.84</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>£12.83</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>£25.32</t>
@@ -705,7 +705,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-ins-board-30mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000021638980E90&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-ins-board-30mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B84D1A10&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -732,34 +732,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>£16.46</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>£16.46</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>£21.95</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>£16.83</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>£16.73</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>£16.73</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>£21.95</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>£16.83</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>£16.73</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>£16.35</t>
@@ -802,7 +802,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-40mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000021635F7B6D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-40mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B7885B10&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -829,54 +829,54 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£17.48</t>
+          <t>£16.70</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£17.48</t>
+          <t>£16.70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>£16.70</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>£20.95</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>£17.93</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>£17.50</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>£18.21</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>£16.75</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>£16.74</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>£20.95</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>£17.93</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>£17.50</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>£18.21</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>£20.49 presale price: £31.68</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>£16.75</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>£16.74</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>£31.90</t>
@@ -899,7 +899,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/50mm-recticel-insulation (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000021638926F10&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/50mm-recticel-insulation (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B592E350&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -926,54 +926,54 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>£21.20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>£21.20</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>£21.20</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>£26.95</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>£21.92</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>£21.65</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>£21.65</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>£22.12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>£26.99 presale price: £39.44</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>£21.45</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>£21.44</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>£26.95</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>£21.92</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>£21.65</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>£22.12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>£26.99 presale price: £39.44</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>£21.45</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>£21.44</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>£37.91</t>
@@ -996,7 +996,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-60mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000216391BBF50&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-60mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B88F94D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1023,54 +1023,54 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>£23.13</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>£23.13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>£23.13</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>£29.95</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>£23.64</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>£23.44</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>£23.44</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>£24.75</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>£30.70 presale price: £45.56</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>£23.16</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>£23.15</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>£29.95</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>£23.64</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>£23.44</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>£24.75</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>£30.70 presale price: £45.56</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>£23.16</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>£23.15</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>£44.99</t>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-70mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000021638B44050&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-70mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B80DC6D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/75mm-recticel-insulation (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000021635F81AD0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/75mm-recticel-insulation (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B585D1D0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-80mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000021638E65450&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-80mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B77F6D90&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1314,54 +1314,54 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>£29.28</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>£29.28</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>£29.28</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>£35.95</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>£29.50</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>£29.36</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>£29.36</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>£30.13</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>£38.75 presale price: £56.64</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>£28.43</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>£29.31</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>£35.95</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>£29.50</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>£29.36</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>£30.13</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>£38.75 presale price: £56.64</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>£28.43</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>£29.31</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>£56.16</t>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-90mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000021638151ED0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-90mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B7F1EBD0&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/100mm-recticel-insulation (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000021638A67E50&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/100mm-recticel-insulation (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B58CE050&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1605,54 +1605,54 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>£35.85</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>£35.85</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>£35.08</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>£44.50</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>£36.46</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>£35.90</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>£35.90</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>£38.42</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>£43.99 presale price: £72.38</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>£35.09</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>£35.08</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>£44.50</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>£36.46</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>£35.90</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>£38.42</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>£43.99 presale price: £72.38</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>£35.09</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>£35.08</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>£70.35</t>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/120mm-recticel-insulation (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000021639296690&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/120mm-recticel-insulation (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B7286E10&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-130mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000021638213090&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-130mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B737AC10&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-140mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000021637DFC610&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/recticel-eurothane-gp-pir-insulation-board-140mm-thick (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B5DE2990&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/150mm-recticel-insulation (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x0000021637BC9390&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.directinsulation.com', port=443): Max retries exceeded with url: /product-page/150mm-recticel-insulation (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x00000224B5B8AD90&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
